--- a/wxdgaming.game.basic/src/main/cfg/怪物信息.xlsx
+++ b/wxdgaming.game.basic/src/main/cfg/怪物信息.xlsx
@@ -159,7 +159,7 @@
     <t>{"MAXHP":100,"体力":100,"攻击":100,"防御":100}</t>
   </si>
   <si>
-    <t>1|10,3|10,5|10</t>
+    <t>1|10#3|10#5|10</t>
   </si>
   <si>
     <t>蜜蜂</t>
@@ -171,7 +171,7 @@
     <t>{"MAXHP":100,"体力":100,"攻击":100,"防御":101}</t>
   </si>
   <si>
-    <t>1|10,3|10,5|11</t>
+    <t>1|10#3|10#5|11</t>
   </si>
   <si>
     <t>蟑螂</t>
@@ -183,7 +183,7 @@
     <t>{"MAXHP":100,"体力":100,"攻击":100,"防御":102}</t>
   </si>
   <si>
-    <t>1|10,3|10,5|12</t>
+    <t>1|10#3|10#5|12</t>
   </si>
   <si>
     <t>黄雀</t>
@@ -195,7 +195,7 @@
     <t>{"MAXHP":100,"体力":100,"攻击":100,"防御":103}</t>
   </si>
   <si>
-    <t>1|10,3|10,5|13</t>
+    <t>1|10#3|10#5|13</t>
   </si>
   <si>
     <t>兔子</t>
@@ -207,7 +207,7 @@
     <t>{"MAXHP":100,"体力":100,"攻击":100,"防御":104}</t>
   </si>
   <si>
-    <t>1|10,3|10,5|14</t>
+    <t>1|10#3|10#5|14</t>
   </si>
   <si>
     <t>公鸡</t>
@@ -219,7 +219,7 @@
     <t>{"MAXHP":100,"体力":100,"攻击":100,"防御":105}</t>
   </si>
   <si>
-    <t>1|10,3|10,5|15</t>
+    <t>1|10#3|10#5|15</t>
   </si>
   <si>
     <t>野狗</t>
@@ -231,7 +231,7 @@
     <t>{"MAXHP":100,"体力":100,"攻击":100,"防御":106}</t>
   </si>
   <si>
-    <t>1|10,3|10,5|16</t>
+    <t>1|10#3|10#5|16</t>
   </si>
   <si>
     <t>小软</t>
@@ -243,7 +243,7 @@
     <t>{"MAXHP":100,"体力":100,"攻击":100,"防御":107}</t>
   </si>
   <si>
-    <t>1|10,3|10,5|17</t>
+    <t>1|10#3|10#5|17</t>
   </si>
   <si>
     <t>猎豹</t>
@@ -255,7 +255,7 @@
     <t>{"MAXHP":100,"体力":100,"攻击":100,"防御":108}</t>
   </si>
   <si>
-    <t>1|10,3|10,5|18</t>
+    <t>1|10#3|10#5|18</t>
   </si>
   <si>
     <t>老虎</t>
@@ -267,7 +267,7 @@
     <t>{"MAXHP":100,"体力":100,"攻击":100,"防御":109}</t>
   </si>
   <si>
-    <t>1|10,3|10,5|19</t>
+    <t>1|10#3|10#5|19</t>
   </si>
   <si>
     <t>蟒蛇</t>
@@ -279,7 +279,7 @@
     <t>{"MAXHP":100,"体力":100,"攻击":100,"防御":110}</t>
   </si>
   <si>
-    <t>1|10,3|10,5|20</t>
+    <t>1|10#3|10#5|20</t>
   </si>
   <si>
     <t>河马</t>
@@ -291,7 +291,7 @@
     <t>{"MAXHP":100,"体力":100,"攻击":100,"防御":111}</t>
   </si>
   <si>
-    <t>1|10,3|10,5|21</t>
+    <t>1|10#3|10#5|21</t>
   </si>
   <si>
     <t>鳄鱼</t>
@@ -303,7 +303,7 @@
     <t>{"MAXHP":100,"体力":100,"攻击":100,"防御":112}</t>
   </si>
   <si>
-    <t>1|10,3|10,5|22</t>
+    <t>1|10#3|10#5|22</t>
   </si>
   <si>
     <t>猛犸象</t>
@@ -315,7 +315,7 @@
     <t>{"MAXHP":100,"体力":100,"攻击":100,"防御":113}</t>
   </si>
   <si>
-    <t>1|10,3|10,5|23</t>
+    <t>1|10#3|10#5|23</t>
   </si>
   <si>
     <t>骷髅头</t>
@@ -327,7 +327,7 @@
     <t>{"MAXHP":100,"体力":100,"攻击":100,"防御":114}</t>
   </si>
   <si>
-    <t>1|10,3|10,5|24</t>
+    <t>1|10#3|10#5|24</t>
   </si>
   <si>
     <t>术士</t>
@@ -339,7 +339,7 @@
     <t>{"MAXHP":100,"体力":100,"攻击":100,"防御":115}</t>
   </si>
   <si>
-    <t>1|10,3|10,5|25</t>
+    <t>1|10#3|10#5|25</t>
   </si>
   <si>
     <t>猎人</t>
@@ -351,7 +351,7 @@
     <t>{"MAXHP":100,"体力":100,"攻击":100,"防御":116}</t>
   </si>
   <si>
-    <t>1|10,3|10,5|26</t>
+    <t>1|10#3|10#5|26</t>
   </si>
   <si>
     <t>刺客</t>
@@ -363,7 +363,7 @@
     <t>{"MAXHP":100,"体力":100,"攻击":100,"防御":117}</t>
   </si>
   <si>
-    <t>1|10,3|10,5|27</t>
+    <t>1|10#3|10#5|27</t>
   </si>
   <si>
     <t>呆呆贼</t>
@@ -375,7 +375,7 @@
     <t>{"MAXHP":100,"体力":100,"攻击":100,"防御":118}</t>
   </si>
   <si>
-    <t>1|10,3|10,5|28</t>
+    <t>1|10#3|10#5|28</t>
   </si>
 </sst>
 </file>
@@ -547,12 +547,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
